--- a/public/files/Data_By_Towns_Index/Burlington/Willingboro Township.xlsx
+++ b/public/files/Data_By_Towns_Index/Burlington/Willingboro Township.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,447 +425,353 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G14"/>
+  <dimension ref="A1:H9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Unnamed: 0</t>
+          <t>Owner Name</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Owner Name</t>
+          <t>Property Location</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Property Location</t>
+          <t>Municipality</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Municipality</t>
+          <t>County</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Search</t>
+          <t>State</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
+          <t>Longitude</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
           <t>Latitude</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Longitude</t>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>PID</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="n">
-        <v>0</v>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>SHAH, MASOOMA R &amp; KHAMIS, SYED</t>
+        </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>MEHTA, DHIREN</t>
+          <t>27 STONEHAVEN LANE</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>17 VAN SCIVER PARKWAY</t>
+          <t>Willingboro Township</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
+          <t>Burlington</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>NJ</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
+        <v>-74.897727</v>
+      </c>
+      <c r="G2" t="n">
+        <v>40.0443845</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>ChIJL3J4rIpLwYkR0A8HIVPN9Lc</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>CHOKSI, NIRAV AND ALISON</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>25 BUCKNELL LANE</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
           <t>Willingboro Township</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Mehta</t>
-        </is>
-      </c>
-      <c r="F2" t="n">
-        <v>40.047976</v>
-      </c>
-      <c r="G2" t="n">
-        <v>-74.885756</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
-        <v>1</v>
-      </c>
-      <c r="B3" t="inlineStr">
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Burlington</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>NJ</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
+        <v>-74.8887393</v>
+      </c>
+      <c r="G3" t="n">
+        <v>40.039911</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>ChIJoTcrHvdLwYkRw7lPUfMy-A0</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>SHARMA, ABHISHEK</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>25 SHERWOOD LANE</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Willingboro Township</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Burlington</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>NJ</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>-74.8891563</v>
+      </c>
+      <c r="G4" t="n">
+        <v>40.0493762</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>ChIJ95nU2w5MwYkR3gmE-P2giyE</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>SHARMA, DENANAUTH &amp; SAVITRIE S</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>50 GARLAND LANE</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Willingboro Township</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Burlington</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>NJ</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>-74.8801574</v>
+      </c>
+      <c r="G5" t="n">
+        <v>40.0268693</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>ChIJcepVrOZLwYkRgLw0pdxdK0I</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>GANDHI, GORANK &amp; ESQUIVEL, EMELIN</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>91 MELBOURNE LANE</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Willingboro Township</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Burlington</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>NJ</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>-74.88646129999999</v>
+      </c>
+      <c r="G6" t="n">
+        <v>40.0212431</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>ChIJg8gl0MJLwYkRnb842d4LEpY</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>PARIKH, HIMANSHU &amp; DIERDRE</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>12 DERRY DRIVE</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Willingboro Township</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Burlington</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>NJ</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>-74.88635379999999</v>
+      </c>
+      <c r="G7" t="n">
+        <v>40.0173577</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>ChIJ91BTsMRLwYkRnqpyVIXJsiA</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
         <is>
           <t>PATEL, ANISH S &amp; POOJA V</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>18 HARRINGTON CIRCLE</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>Willingboro Township</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Patel</t>
-        </is>
-      </c>
-      <c r="F3" t="n">
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Burlington</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>NJ</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>-74.8683255</v>
+      </c>
+      <c r="G8" t="n">
         <v>40.0288986</v>
       </c>
-      <c r="G3" t="n">
-        <v>-74.8683255</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>2</v>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>PATEL, BHAILAL L &amp; SAVITA B</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>4272 ROUTE 130</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>ChIJNekciFlJwYkRN7Tn3yFMbxY</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>PATEL, DEEPIKA</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>15 NOLAND LANE</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
         <is>
           <t>Willingboro Township</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Patel</t>
-        </is>
-      </c>
-      <c r="F4" t="n">
-        <v>40.0441012</v>
-      </c>
-      <c r="G4" t="n">
-        <v>-74.90649049999999</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>3</v>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>PATEL, DEEPIKA</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>15 NOLAND LANE</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Willingboro Township</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Patel</t>
-        </is>
-      </c>
-      <c r="F5" t="n">
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Burlington</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>NJ</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>-74.86167689999999</v>
+      </c>
+      <c r="G9" t="n">
         <v>40.0279648</v>
       </c>
-      <c r="G5" t="n">
-        <v>-74.86167689999999</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>4</v>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>PATEL, MAHESH J</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>31 SANDAL LANE</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Willingboro Township</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Patel</t>
-        </is>
-      </c>
-      <c r="F6" t="n">
-        <v>40.0516525</v>
-      </c>
-      <c r="G6" t="n">
-        <v>-74.8819566</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>5</v>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>SHAH, AMITKUMAR</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>77 RITTENHOUSE DRIVE</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Willingboro Township</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>Shah</t>
-        </is>
-      </c>
-      <c r="F7" t="n">
-        <v>40.0356079</v>
-      </c>
-      <c r="G7" t="n">
-        <v>-74.9107496</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>6</v>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>SHAH, KUSH &amp; BARVALLA, UJAAS ET AL</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>94 BAYBERRY LANE</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Willingboro Township</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>Shah</t>
-        </is>
-      </c>
-      <c r="F8" t="n">
-        <v>40.0358224</v>
-      </c>
-      <c r="G8" t="n">
-        <v>-74.87988249999999</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>7</v>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>SHAH, MASOOMA R &amp; KHAMIS, SYED</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>27 STONEHAVEN LANE</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Willingboro Township</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>Shah</t>
-        </is>
-      </c>
-      <c r="F9" t="n">
-        <v>40.0443845</v>
-      </c>
-      <c r="G9" t="n">
-        <v>-74.897727</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>8</v>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>SHAH,ILYAS &amp; ERD NJ INVESTMENTS LLC</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>4412 ROUTE 130</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Willingboro Township</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>Shah</t>
-        </is>
-      </c>
-      <c r="F10" t="n">
-        <v>40.0571097</v>
-      </c>
-      <c r="G10" t="n">
-        <v>-74.88657529999999</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>9</v>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>SHARMA, DENANAUTH &amp; SAVITRIE S</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>50 GARLAND LANE</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Willingboro Township</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>Sharma</t>
-        </is>
-      </c>
-      <c r="F11" t="n">
-        <v>40.0268693</v>
-      </c>
-      <c r="G11" t="n">
-        <v>-74.8801574</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>10</v>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>CHOKSI, NIRAV AND ALISON</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>25 BUCKNELL LANE</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Willingboro Township</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>Choksi</t>
-        </is>
-      </c>
-      <c r="F12" t="n">
-        <v>40.039911</v>
-      </c>
-      <c r="G12" t="n">
-        <v>-74.8887393</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>11</v>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>GANDHI, GORANK &amp; ESQUIVEL, EMELIN</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>91 MELBOURNE LANE</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Willingboro Township</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>Gandhi</t>
-        </is>
-      </c>
-      <c r="F13" t="n">
-        <v>40.0212431</v>
-      </c>
-      <c r="G13" t="n">
-        <v>-74.88646129999999</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>12</v>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>PARIKH, HIMANSHU &amp; DIERDRE</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>12 DERRY DRIVE</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>Willingboro Township</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>Parikh</t>
-        </is>
-      </c>
-      <c r="F14" t="n">
-        <v>40.0173577</v>
-      </c>
-      <c r="G14" t="n">
-        <v>-74.88635379999999</v>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>ChIJt374L0VJwYkRaLhF50Hs6Sw</t>
+        </is>
       </c>
     </row>
   </sheetData>
